--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00710B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00710B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53D9454F-B181-4F2F-8B1A-108DE3FBC720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{276A08EE-01B2-4E76-9783-112B2666D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{57A9A2FB-E712-4C75-8AB4-F3ECE12FE346}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{553152B6-CDEA-4F11-878F-A2B7CE8AE51F}"/>
   </bookViews>
   <sheets>
     <sheet name="00710B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1595,25 +1595,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404BBCD2-EF1D-4265-B744-0D116E9002EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{813ABEFE-2647-4D42-A2B3-824E31A2B0B7}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1671,7 +1671,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1767,7 +1767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2019</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2018</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>25</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>25</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>25</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>25</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>25</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2017</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>25</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
         <v>84</v>
       </c>
